--- a/tests/realSuite/Piano-Viaggi-Corsa-Campestre_IC_Ragazz-_14-marzo-25-2/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi-Corsa-Campestre_IC_Ragazz-_14-marzo-25-2/input.xlsx
@@ -996,7 +996,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Stazione autocorriere, Fiera di Primiero</t>
+          <t>38054 Fiera di Primiero TN</t>
         </is>
       </c>
       <c r="C39" t="n">

--- a/tests/realSuite/Piano-Viaggi-Corsa-Campestre_IC_Ragazz-_14-marzo-25-2/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi-Corsa-Campestre_IC_Ragazz-_14-marzo-25-2/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -996,7 +996,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>38054 Fiera di Primiero TN</t>
+          <t>Stazione autocorriere, Fiera di Primiero</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1111,42 +1111,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>IC TRENTO 5</t>
+          <t>IC TRENTO 3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fermata bus Funivia Trento/Sardagna, Trento</t>
+          <t>Fermata Bus Funivia, Trento</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IC TRENTO 7</t>
+          <t>IC TRENTO 5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Posteggio Centro Sportivo Trento Nord, Via Don Milani, Gardolo</t>
+          <t>Fermata bus Funivia Trento/Sardagna, Trento</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IC TRENTO ARCIVESCOVILE</t>
+          <t>IC TRENTO 6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fermata Bus Funivia, Trento</t>
+          <t>Fermata bus Funivia Trento/Sardagna, Trento</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1156,31 +1156,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC TRENTO 7</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fermata bus – Piazza Palù, Madonna di Campiglio</t>
+          <t>Posteggio Centro Sportivo Trento Nord, Via Don Milani, Gardolo</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC TRENTO ARCIVESCOVILE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SSPG – Viale della Pace, 10, Pinzolo</t>
+          <t>Fermata Bus Funivia, Trento</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
@@ -1191,41 +1191,41 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SSPG, Spiazzo Rendena</t>
+          <t>Fermata bus – Piazza Palù, Madonna di Campiglio</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>IC VALLE DEI LAGHI-DRO</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fermata bus c/o farmacia - Via Roma, Vezzano</t>
+          <t>SSPG – Viale della Pace, 10, Pinzolo</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IC VALLE DEI LAGHI-DRO</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Piazza centrale, Cavedine</t>
+          <t>SSPG, Spiazzo Rendena</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -1236,41 +1236,86 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SSPG - Via S. Antonio, 3, Dro</t>
+          <t>Fermata bus c/o farmacia - Via Roma, Vezzano</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IC VALLE DI LEDRO</t>
+          <t>IC VALLE DEI LAGHI-DRO</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SSPG - Via Falcone e Borsellino, 2, Ledro/Bezzecca</t>
+          <t>Piazza centrale, Cavedine</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>IC VALLE DEI LAGHI-DRO</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SSPG - Via S. Antonio, 3, Dro</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>IC VALLE DI LEDRO</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SSPG - Via Falcone e Borsellino, 2, Ledro/Bezzecca</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>IC VIGOLO VATTARO</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Fermata bus, Vigolo Vattaro</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C59" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Students staff IS TIONE GUETTI</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SSPG – Via Circonvallazione, 44, Tione</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/tests/realSuite/Piano-Viaggi-Corsa-Campestre_IC_Ragazz-_14-marzo-25-2/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi-Corsa-Campestre_IC_Ragazz-_14-marzo-25-2/input.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Scuola primaria – Via Betta, Ala</t>
+          <t>Scuola primaria "Abramo Betta", 9, Via Abramo Betta, Ala, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38061, Italia</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/tests/realSuite/Piano-Viaggi-Corsa-Campestre_IC_Ragazz-_14-marzo-25-2/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi-Corsa-Campestre_IC_Ragazz-_14-marzo-25-2/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC ALDENO-MATTARELLO</t>
+          <t>IC ALTA VALLAGARINA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fermata bus Al Parco – Via Torre Franca, Mattarello</t>
+          <t>Scuola Elementare Giangrisostomo Tovazzi, 30, Via Stazione, Volano, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38060, Italia</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -466,192 +466,192 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC ALDENO-MATTARELLO</t>
+          <t>IC BASSA ANAUNIA-TUENNO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fermata bus – Via Filzi, Aldeno</t>
+          <t>SSPG - Via V. Maistrelli, 10, Tuenno</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC ALTA VALLAGARINA</t>
+          <t>IC BASSA VAL DI SOLE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fermata bus - Piazzale Orsi, Rovereto</t>
+          <t>Nuova stazione FTM, Malè</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC ALTOPIANO DI PINE’</t>
+          <t>IC BRENTONICO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SSPG - Via del 26 maggio, 6, Baselga di Pinè</t>
+          <t>SSPG - Via F. Calzolari, 2, Brentonico</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC ARCO</t>
+          <t>IC CAVALESE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SSPG – Loc. Prabi, Arco</t>
+          <t>SSPG – Fermata bus – Piazza Verdi, Cavalese</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC BASSA ANAUNIA-TUENNO</t>
+          <t>IC CEMBRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SSPG - Via Colle Verde, 3, Denno</t>
+          <t>SSPG – Loc. Scancio, 68, Segonzano</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC BASSA ANAUNIA-TUENNO</t>
+          <t>IC CEMBRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SSPG - Via V. Maistrelli, 10, Tuenno</t>
+          <t>SSPG – Via Negritelle, Cembra</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC BASSA VAL DI SOLE</t>
+          <t>IC CEMBRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nuova stazione FTM, Malè</t>
+          <t>SSPG – Via Oratorio, 15, Verla di Giovo</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC BRENTONICO</t>
+          <t>IC CENTRO VALSUGANA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SSPG - Via F. Calzolari, 2, Brentonico</t>
+          <t>Fermata bus Piazza Maggiore, Telve</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC CAVALESE</t>
+          <t>IC CENTRO VALSUGANA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SSPG – Fermata bus – Piazza Verdi, Cavalese</t>
+          <t>Park Pizzeria Picchio, Via Battisti, Roncegno</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC CEMBRA</t>
+          <t>IC CHIESE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SSPG – Loc. Scancio, 68, Segonzano</t>
+          <t>SSPG - Via Papaleoni, 5, Storo</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC CEMBRA</t>
+          <t>IC CHIESE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SSPG – Via Negritelle, Cembra</t>
+          <t>SSPG - Via alla Fiera, 1, Pieve di Bono</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC CEMBRA</t>
+          <t>IC CIVEZZANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SSPG – Via Oratorio, 15, Verla di Giovo</t>
+          <t>Via Murialdo 27, Civezzano</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC CENTRO VALSUGANA</t>
+          <t>IC FOLGARIA-LAV.-LUS.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fermata bus Piazza Maggiore, Telve</t>
+          <t>Palazzo del ghiaccio, Folgaria</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -661,12 +661,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC CENTRO VALSUGANA</t>
+          <t>IC FOLGARIA-LAV.-LUS.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Park Pizzeria Picchio, Via Battisti, Roncegno</t>
+          <t>Polo scolastico – Frazione Gionghi, Lavarone</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -676,222 +676,222 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC CHIESE</t>
+          <t>IC FONDO-REVO’</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SSPG - Via Papaleoni, 5, Storo</t>
+          <t>Fermata bus – Via Canestrini, Revò</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC CHIESE</t>
+          <t>IC FONDO-REVO’</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SSPG - Via alla Fiera, 1, Pieve di Bono</t>
+          <t>SSPG - Via G. Garibaldi, 24, Fondo</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC CIVEZZANO</t>
+          <t>IC GIUDICARIE ESTERIORI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Via Murialdo 27, Civezzano</t>
+          <t>SSPG – Via San Giovanni Bosco, 14, Ponte Arche</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC FOLGARIA-LAV.-LUS.</t>
+          <t>IC LADINO DI FASSA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Palazzo del ghiaccio, Folgaria</t>
+          <t>Fermata bus Te volto, Moena</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC FOLGARIA-LAV.-LUS.</t>
+          <t>IC LADINO DI FASSA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Polo scolastico – Frazione Gionghi, Lavarone</t>
+          <t>Piaz de Ciampedel, Campitello di Fassa</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC FONDO-REVO’</t>
+          <t>IC LADINO DI FASSA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fermata bus – Via Canestrini, Revò</t>
+          <t>Via G. Soraperra, 6, Sen Jan</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IC FONDO-REVO’</t>
+          <t>IC LAVIS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SSPG - Via G. Garibaldi, 24, Fondo</t>
+          <t>SSPG - Via Carlo Sette, 13/a, Lavis</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IC GIUDICARIE ESTERIORI</t>
+          <t>IC LEVICO TERME</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SSPG – Via San Giovanni Bosco, 14, Ponte Arche</t>
+          <t>Scuola Via della Pace, Levico Terme</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IC LADINO DI FASSA</t>
+          <t>IC MEZZANO Santa Croce</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fermata bus Te volto, Moena</t>
+          <t>Via Molaren, Mezzano</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IC LADINO DI FASSA</t>
+          <t>IC MEZZOCORONA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Piaz de Ciampedel, Campitello di Fassa</t>
+          <t>SSPG - Via Fornai, 1, Mezzocorona</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IC LADINO DI FASSA</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Via G. Soraperra, 6, Sen Jan</t>
+          <t>Fermata bus, Spormaggiore</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IC LAVIS</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SSPG - Via Carlo Sette, 13/a, Lavis</t>
+          <t>Piazza San Vito, 1, Andalo</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IC LEVICO TERME</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Scuola Via della Pace, Levico Terme</t>
+          <t>SSPG - Via degli Alpini, 17, Mezzolombardo</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IC MEZZANO Santa Croce</t>
+          <t>IC MORI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Via Molaren, Mezzano</t>
+          <t>SSPG - Via Giovanni XXIII, 64, Mori</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IC MEZZOCORONA</t>
+          <t>IC PERGINE 1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SSPG - Via Fornai, 1, Mezzocorona</t>
+          <t>SSPG – Via Caduti, 39, Pergine Valsugana</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -901,72 +901,72 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC PERGINE 2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fermata bus, Spormaggiore</t>
+          <t>Fermata bus – Viale Dante (Tentazioni), Pergine Valsugana</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC PRIMIERO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Piazza San Vito, 1, Andalo</t>
+          <t>Stazione autocorriere, Fiera di Primiero</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC RIVA 1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SSPG - Via degli Alpini, 17, Mezzolombardo</t>
+          <t>Viale Damiano Chiesa 12, Riva del Garda</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IC MORI</t>
+          <t>IC RIVA 2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SSPG - Via Giovanni XXIII, 64, Mori</t>
+          <t>Centro Sportivo Malossini - Via Ginestre 1, Riva del Garda</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IC PERGINE 1</t>
+          <t>IC ROVERETO EST</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SSPG – Via Caduti, 39, Pergine Valsugana</t>
+          <t>Piazzale Orsi, Rovereto</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -976,72 +976,72 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IC PERGINE 2</t>
+          <t>IC ROVERETO NORD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fermata bus – Viale Dante (Tentazioni), Pergine Valsugana</t>
+          <t>Piazzale Orsi, Rovereto</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IC PRIMIERO</t>
+          <t>IC STRIGNO-TESINO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Stazione autocorriere, Fiera di Primiero</t>
+          <t>SSPG - Fermata bus - Via Roma, Castel Ivano/Strigno</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IC RIVA 1</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Viale Damiano Chiesa 12, Riva del Garda</t>
+          <t>SSPG – Via Circonvallazione, 44, Tione</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IC RIVA 2</t>
+          <t>IC TRENTO 2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Centro Sportivo Malossini - Via Ginestre 1, Riva del Garda</t>
+          <t>SSPG - Via Ponte Alto, 2/1, Trento/Cognola</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IC ROVERETO EST</t>
+          <t>IC TRENTO 3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Piazzale Orsi, Rovereto</t>
+          <t>Fermata Bus Funivia, Trento</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1051,27 +1051,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IC ROVERETO NORD</t>
+          <t>IC TRENTO 5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Piazzale Orsi, Rovereto</t>
+          <t>Fermata bus Funivia Trento/Sardagna, Trento</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IC STRIGNO-TESINO</t>
+          <t>IC TRENTO 6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SSPG - Fermata bus - Via Roma, Castel Ivano/Strigno</t>
+          <t>Fermata bus Funivia Trento/Sardagna, Trento</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1081,27 +1081,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC TRENTO 7</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SSPG – Via Circonvallazione, 44, Tione</t>
+          <t>Posteggio Centro Sportivo Trento Nord, Via Don Milani, Gardolo</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IC TRENTO 2</t>
+          <t>IC TRENTO ARCIVESCOVILE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SSPG - Via Ponte Alto, 2/1, Trento/Cognola</t>
+          <t>Fermata Bus Funivia, Trento</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1111,12 +1111,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>IC TRENTO 3</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fermata Bus Funivia, Trento</t>
+          <t>Fermata bus – Piazza Palù, Madonna di Campiglio</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1126,195 +1126,120 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IC TRENTO 5</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fermata bus Funivia Trento/Sardagna, Trento</t>
+          <t>SSPG – Viale della Pace, 10, Pinzolo</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IC TRENTO 6</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fermata bus Funivia Trento/Sardagna, Trento</t>
+          <t>SSPG, Spiazzo Rendena</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IC TRENTO 7</t>
+          <t>IC VALLE DEI LAGHI-DRO</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Posteggio Centro Sportivo Trento Nord, Via Don Milani, Gardolo</t>
+          <t>Fermata bus c/o farmacia - Via Roma, Vezzano</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>IC TRENTO ARCIVESCOVILE</t>
+          <t>IC VALLE DEI LAGHI-DRO</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fermata Bus Funivia, Trento</t>
+          <t>Piazza centrale, Cavedine</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC VALLE DEI LAGHI-DRO</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fermata bus – Piazza Palù, Madonna di Campiglio</t>
+          <t>SSPG - Via S. Antonio, 3, Dro</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC VALLE DI LEDRO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SSPG – Viale della Pace, 10, Pinzolo</t>
+          <t>SSPG - Via Falcone e Borsellino, 2, Ledro/Bezzecca</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC VIGOLO VATTARO</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SSPG, Spiazzo Rendena</t>
+          <t>Fermata bus, Vigolo Vattaro</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IC VALLE DEI LAGHI-DRO</t>
+          <t>Students staff IS TIONE GUETTI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fermata bus c/o farmacia - Via Roma, Vezzano</t>
+          <t>SSPG – Via Circonvallazione, 44, Tione</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>IC VALLE DEI LAGHI-DRO</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Piazza centrale, Cavedine</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>IC VALLE DEI LAGHI-DRO</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>SSPG - Via S. Antonio, 3, Dro</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>IC VALLE DI LEDRO</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>SSPG - Via Falcone e Borsellino, 2, Ledro/Bezzecca</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>IC VIGOLO VATTARO</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Fermata bus, Vigolo Vattaro</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Students staff IS TIONE GUETTI</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>SSPG – Via Circonvallazione, 44, Tione</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
         <v>16</v>
       </c>
     </row>
